--- a/KS_folding_tests/comparing.xlsx
+++ b/KS_folding_tests/comparing.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOUTORADO\units\XAI4Spectra\KS_folding_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CE028D-9AD8-473D-8BA4-F24A082561CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F38D8C-95F1-4A0D-9791-C30C8C6369D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="synthetic" sheetId="2" r:id="rId1"/>
-    <sheet name="soil type" sheetId="1" r:id="rId2"/>
-    <sheet name="bank_notes" sheetId="3" r:id="rId3"/>
-    <sheet name="soil" sheetId="4" r:id="rId4"/>
+    <sheet name="synthetic_dataset" sheetId="2" r:id="rId1"/>
+    <sheet name="bank_notes" sheetId="3" r:id="rId2"/>
+    <sheet name="soil type" sheetId="1" r:id="rId3"/>
+    <sheet name="soil fertility" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="53">
   <si>
     <t>Vip</t>
   </si>
@@ -124,12 +124,6 @@
     <t>RBO_Score</t>
   </si>
   <si>
-    <t>fold_rank</t>
-  </si>
-  <si>
-    <t>cooccurence</t>
-  </si>
-  <si>
     <t>F1</t>
   </si>
   <si>
@@ -160,12 +154,6 @@
     <t>background1</t>
   </si>
   <si>
-    <t>cooc</t>
-  </si>
-  <si>
-    <t>rank</t>
-  </si>
-  <si>
     <t>Ag ka scattering</t>
   </si>
   <si>
@@ -185,6 +173,15 @@
   </si>
   <si>
     <t>background10</t>
+  </si>
+  <si>
+    <t>peso no grafo = ranking score</t>
+  </si>
+  <si>
+    <t>peso no grafo = cooccurrence * confidence score</t>
+  </si>
+  <si>
+    <t>bagging com 20 bags</t>
   </si>
 </sst>
 </file>
@@ -232,7 +229,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -255,11 +252,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -286,6 +292,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -593,17 +602,26 @@
   <dimension ref="A1:O26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="10" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="11" width="13.6640625" style="2" customWidth="1"/>
     <col min="12" max="13" width="8.88671875" style="2"/>
-    <col min="14" max="15" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="2" customWidth="1"/>
     <col min="16" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="E1" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="D1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -651,37 +669,37 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>0</v>
@@ -695,37 +713,37 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>0</v>
@@ -739,37 +757,37 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="D5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="G5" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>0</v>
@@ -783,37 +801,37 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="J6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>0</v>
@@ -827,37 +845,37 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>0</v>
@@ -871,37 +889,37 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>0</v>
@@ -921,13 +939,13 @@
         <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>19</v>
@@ -936,13 +954,13 @@
         <v>19</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>19</v>
@@ -959,34 +977,34 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>23</v>
@@ -1009,10 +1027,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>23</v>
@@ -1021,19 +1039,19 @@
         <v>23</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="J11" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>0</v>
@@ -1047,37 +1065,37 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="G12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>0</v>
@@ -1090,9 +1108,18 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="E15" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="D15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -1140,37 +1167,37 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>0</v>
@@ -1184,37 +1211,37 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="I18" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>0</v>
@@ -1228,37 +1255,37 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="D19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="F19" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>0</v>
@@ -1272,37 +1299,37 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="J20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>0</v>
@@ -1316,37 +1343,37 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>0</v>
@@ -1360,37 +1387,37 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>0</v>
@@ -1410,7 +1437,7 @@
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>19</v>
@@ -1422,7 +1449,7 @@
         <v>19</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>23</v>
@@ -1431,7 +1458,7 @@
         <v>23</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>19</v>
@@ -1448,34 +1475,34 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="G24" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>23</v>
@@ -1498,31 +1525,31 @@
         <v>23</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="I25" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>0</v>
@@ -1536,16 +1563,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>23</v>
@@ -1554,19 +1581,19 @@
         <v>23</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>0</v>
@@ -1579,26 +1606,1056 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I15:K15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A07658-2066-41F0-8B01-FBEDD8313F2D}">
+  <dimension ref="A1:O26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="14.33203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3">
+        <v>0.92226877176333333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>0.91507587997333339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" t="s">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5">
+        <v>0.91386527176333343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>10</v>
+      </c>
+      <c r="O6">
+        <v>0.87326877176333328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7">
+        <v>0.86295538030666663</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8">
+        <v>0.7682687717633333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>2</v>
+      </c>
+      <c r="O9">
+        <v>0.46401428551333329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" t="s">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <v>0.39959148030666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" t="s">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11">
+        <v>0.26573427176333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" t="s">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0.23575478551333329</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M17" t="s">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>9</v>
+      </c>
+      <c r="O17">
+        <v>0.92226877176333333</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" t="s">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18">
+        <v>0.91386527176333343</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="M19" t="s">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19">
+        <v>0.91386527176333343</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="M20" t="s">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>10</v>
+      </c>
+      <c r="O20">
+        <v>0.87326877176333328</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" t="s">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21">
+        <v>0.86799748030666668</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" t="s">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>7</v>
+      </c>
+      <c r="O22">
+        <v>0.82473427176333336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>6</v>
+      </c>
+      <c r="O23">
+        <v>0.80886527176333345</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24">
+        <v>0.54035087997333331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>2</v>
+      </c>
+      <c r="O25">
+        <v>0.46401428551333329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>0.23575478551333329</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="11" width="14.33203125" style="2" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="E1" s="2" t="s">
-        <v>34</v>
-      </c>
+    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -2084,10 +3141,19 @@
         <v>0.51756428551333333</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="E15" s="2" t="s">
-        <v>33</v>
-      </c>
+    <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -2574,1003 +3640,13 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I15:K15"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A07658-2066-41F0-8B01-FBEDD8313F2D}">
-  <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="5" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="E1" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" t="s">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3">
-        <v>0.92226877176333333</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" t="s">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>5</v>
-      </c>
-      <c r="O4">
-        <v>0.91507587997333339</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" t="s">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>8</v>
-      </c>
-      <c r="O5">
-        <v>0.91386527176333343</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>10</v>
-      </c>
-      <c r="O6">
-        <v>0.87326877176333328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" t="s">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7">
-        <v>0.86295538030666663</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" t="s">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>6</v>
-      </c>
-      <c r="O8">
-        <v>0.7682687717633333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>2</v>
-      </c>
-      <c r="O9">
-        <v>0.46401428551333329</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O10">
-        <v>0.39959148030666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" t="s">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>7</v>
-      </c>
-      <c r="O11">
-        <v>0.26573427176333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>0.23575478551333329</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="E15" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M17" t="s">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>9</v>
-      </c>
-      <c r="O17">
-        <v>0.92226877176333333</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M18" t="s">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18">
-        <v>0.91386527176333343</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="M19" t="s">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>8</v>
-      </c>
-      <c r="O19">
-        <v>0.91386527176333343</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M20" t="s">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>10</v>
-      </c>
-      <c r="O20">
-        <v>0.87326877176333328</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" t="s">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21">
-        <v>0.86799748030666668</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M22" t="s">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>7</v>
-      </c>
-      <c r="O22">
-        <v>0.82473427176333336</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23" t="s">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>6</v>
-      </c>
-      <c r="O23">
-        <v>0.80886527176333345</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24">
-        <v>0.54035087997333331</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O25">
-        <v>0.46401428551333329</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M26" t="s">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <v>0.23575478551333329</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3579,19 +3655,25 @@
   <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="11" width="13.6640625" style="2" customWidth="1"/>
     <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="E1" s="2" t="s">
-        <v>34</v>
-      </c>
+    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -3748,7 +3830,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>25</v>
@@ -3836,7 +3918,7 @@
         <v>15</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>20</v>
@@ -3862,7 +3944,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>25</v>
@@ -3889,7 +3971,7 @@
         <v>21</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M8" t="s">
         <v>0</v>
@@ -3915,7 +3997,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>20</v>
@@ -3927,10 +4009,10 @@
         <v>11</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>15</v>
@@ -3962,7 +4044,7 @@
         <v>27</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>25</v>
@@ -3994,10 +4076,10 @@
         <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>23</v>
@@ -4041,7 +4123,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>18</v>
@@ -4050,10 +4132,10 @@
         <v>15</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>16</v>
@@ -4077,10 +4159,19 @@
         <v>0.26069217176333331</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="E14" s="2" t="s">
-        <v>33</v>
-      </c>
+    <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -4351,7 +4442,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
@@ -4369,7 +4460,7 @@
         <v>14</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>18</v>
@@ -4378,7 +4469,7 @@
         <v>21</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M21" t="s">
         <v>0</v>
@@ -4416,10 +4507,10 @@
         <v>16</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>15</v>
@@ -4451,13 +4542,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>21</v>
@@ -4483,10 +4574,10 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>18</v>
@@ -4498,7 +4589,7 @@
         <v>17</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>20</v>
@@ -4530,7 +4621,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>20</v>
@@ -4567,6 +4658,12 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="I14:K14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>